--- a/data/trans_orig/P57_AC_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57_AC_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2007</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>292557</t>
+          <t>292090</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>333130</t>
+          <t>335037</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>182969</t>
+          <t>182504</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>216718</t>
+          <t>217177</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>484876</t>
+          <t>483494</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>539565</t>
+          <t>539045</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139562</t>
+          <t>137655</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>180135</t>
+          <t>180602</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88811</t>
+          <t>88352</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122560</t>
+          <t>123025</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>238656</t>
+          <t>239176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>293345</t>
+          <t>294727</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>206133</t>
+          <t>206075</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>244746</t>
+          <t>244730</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>227423</t>
+          <t>226313</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>262392</t>
+          <t>262971</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>445597</t>
+          <t>443766</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>497031</t>
+          <t>497618</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,5%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>120638</t>
+          <t>120654</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>159251</t>
+          <t>159309</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>109473</t>
+          <t>108894</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>144442</t>
+          <t>145552</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>240218</t>
+          <t>239631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>291652</t>
+          <t>293483</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,81%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>365391</t>
+          <t>365931</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>407875</t>
+          <t>408983</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103718</t>
+          <t>104653</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127266</t>
+          <t>127601</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>482327</t>
+          <t>481413</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>532235</t>
+          <t>531041</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,88%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134514</t>
+          <t>133406</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>176998</t>
+          <t>176458</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39536</t>
+          <t>39201</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63084</t>
+          <t>62149</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>176956</t>
+          <t>178150</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>226864</t>
+          <t>227778</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>843898</t>
+          <t>840661</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>907626</t>
+          <t>903540</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>499023</t>
+          <t>496298</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>546446</t>
+          <t>545499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1356115</t>
+          <t>1358447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1434396</t>
+          <t>1440274</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,76%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>330708</t>
+          <t>334794</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>394436</t>
+          <t>397673</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>167839</t>
+          <t>168786</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>215262</t>
+          <t>217987</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>518224</t>
+          <t>512346</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>596505</t>
+          <t>594173</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>230935</t>
+          <t>230694</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>265504</t>
+          <t>265166</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>420650</t>
+          <t>420331</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>459570</t>
+          <t>459754</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>662563</t>
+          <t>663184</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>715891</t>
+          <t>716066</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,89%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85051</t>
+          <t>85389</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119620</t>
+          <t>119861</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109182</t>
+          <t>108998</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148102</t>
+          <t>148421</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>203416</t>
+          <t>203241</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>256744</t>
+          <t>256123</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>151688</t>
+          <t>152062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>184993</t>
+          <t>184642</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>830593</t>
+          <t>831534</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>895403</t>
+          <t>894204</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>995265</t>
+          <t>991449</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1067091</t>
+          <t>1067722</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,02%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113208</t>
+          <t>113559</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>146513</t>
+          <t>146139</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>353357</t>
+          <t>354556</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>418167</t>
+          <t>417226</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>479869</t>
+          <t>479238</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>551695</t>
+          <t>555511</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2171123</t>
+          <t>2164272</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2277494</t>
+          <t>2272478</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2334801</t>
+          <t>2333578</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2438598</t>
+          <t>2437570</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4533373</t>
+          <t>4530105</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4690545</t>
+          <t>4685517</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,53%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>990062</t>
+          <t>995078</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1096433</t>
+          <t>1103284</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>937395</t>
+          <t>938423</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1041192</t>
+          <t>1042415</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1953004</t>
+          <t>1958032</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2110176</t>
+          <t>2113444</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2012</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2012 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>254129</t>
+          <t>253895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>296731</t>
+          <t>296733</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>191944</t>
+          <t>190431</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>227156</t>
+          <t>226635</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>458311</t>
+          <t>457014</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>514791</t>
+          <t>513394</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,69%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139432</t>
+          <t>139430</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>182034</t>
+          <t>182268</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84081</t>
+          <t>84602</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>119293</t>
+          <t>120806</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>232609</t>
+          <t>234006</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>289089</t>
+          <t>290386</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>253853</t>
+          <t>251538</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>293386</t>
+          <t>293779</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>215992</t>
+          <t>217247</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>252755</t>
+          <t>252319</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>481331</t>
+          <t>481551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>534097</t>
+          <t>536009</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,36%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>123382</t>
+          <t>122989</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>162915</t>
+          <t>165230</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81593</t>
+          <t>82029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118356</t>
+          <t>117101</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>217020</t>
+          <t>215108</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>269786</t>
+          <t>269566</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,89%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>384715</t>
+          <t>388124</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>433932</t>
+          <t>435708</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>165224</t>
+          <t>165518</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195027</t>
+          <t>194910</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>558900</t>
+          <t>561434</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>617471</t>
+          <t>617736</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,97%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>189790</t>
+          <t>188014</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>239007</t>
+          <t>235598</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64166</t>
+          <t>64283</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93969</t>
+          <t>93675</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265443</t>
+          <t>265178</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>324014</t>
+          <t>321480</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>746432</t>
+          <t>750355</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>811417</t>
+          <t>814090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>569421</t>
+          <t>568722</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>617281</t>
+          <t>616347</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1332695</t>
+          <t>1332078</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1415420</t>
+          <t>1410372</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,73%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>337687</t>
+          <t>335014</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>402672</t>
+          <t>398749</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146380</t>
+          <t>147314</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>194240</t>
+          <t>194939</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>497345</t>
+          <t>502393</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>580070</t>
+          <t>580687</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>334666</t>
+          <t>333162</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>376414</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>552978</t>
+          <t>549663</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>599023</t>
+          <t>599999</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>901967</t>
+          <t>896686</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>963695</t>
+          <t>960527</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,13%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126967</t>
+          <t>128583</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168715</t>
+          <t>170219</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>159281</t>
+          <t>158305</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205326</t>
+          <t>208641</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>297991</t>
+          <t>301159</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359719</t>
+          <t>365000</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>142005</t>
+          <t>142334</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>173521</t>
+          <t>174258</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>757929</t>
+          <t>756422</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>816866</t>
+          <t>819600</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>911554</t>
+          <t>908097</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>980771</t>
+          <t>980999</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,64%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>91470</t>
+          <t>90733</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>122986</t>
+          <t>122657</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>287408</t>
+          <t>284674</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>346345</t>
+          <t>347852</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>388494</t>
+          <t>388266</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>457711</t>
+          <t>461168</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2198921</t>
+          <t>2202311</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2310314</t>
+          <t>2312745</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2528920</t>
+          <t>2526548</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2636408</t>
+          <t>2641447</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4763928</t>
+          <t>4760969</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4912896</t>
+          <t>4926007</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,13%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1083814</t>
+          <t>1081383</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1195207</t>
+          <t>1191817</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>894610</t>
+          <t>889571</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1002098</t>
+          <t>1004470</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2012251</t>
+          <t>1999140</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2161219</t>
+          <t>2164178</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2016</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2016 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>306717</t>
+          <t>306896</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>341218</t>
+          <t>344199</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>250244</t>
+          <t>249853</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>281714</t>
+          <t>282294</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>569517</t>
+          <t>569074</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>619250</t>
+          <t>617213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,82%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87009</t>
+          <t>84028</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>121510</t>
+          <t>121331</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63363</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94833</t>
+          <t>95224</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154054</t>
+          <t>156091</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>203787</t>
+          <t>204230</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>260588</t>
+          <t>260613</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>294544</t>
+          <t>294364</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>269849</t>
+          <t>272515</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>303072</t>
+          <t>304922</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>540273</t>
+          <t>539611</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>586653</t>
+          <t>587639</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,05%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78554</t>
+          <t>78734</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>112510</t>
+          <t>112485</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67235</t>
+          <t>65385</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100458</t>
+          <t>97792</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>156752</t>
+          <t>155766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>203132</t>
+          <t>203794</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>419501</t>
+          <t>420441</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>453568</t>
+          <t>454563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128926</t>
+          <t>129202</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>147854</t>
+          <t>147939</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>559312</t>
+          <t>557726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>595923</t>
+          <t>596096</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,21%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67380</t>
+          <t>66385</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101447</t>
+          <t>100507</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14730</t>
+          <t>14645</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33658</t>
+          <t>33382</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87609</t>
+          <t>87436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124220</t>
+          <t>125806</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>877699</t>
+          <t>877575</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>931316</t>
+          <t>931540</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>662944</t>
+          <t>663451</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>706882</t>
+          <t>705770</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1552624</t>
+          <t>1553431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1627439</t>
+          <t>1622183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>212081</t>
+          <t>211857</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>265698</t>
+          <t>265822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>115309</t>
+          <t>116421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159247</t>
+          <t>158740</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>338149</t>
+          <t>343405</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>412964</t>
+          <t>412157</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>473981</t>
+          <t>477104</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>515484</t>
+          <t>517593</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>602007</t>
+          <t>602963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>640260</t>
+          <t>640396</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1090220</t>
+          <t>1088586</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1146094</t>
+          <t>1143133</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100022</t>
+          <t>97913</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>141525</t>
+          <t>138402</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92896</t>
+          <t>92760</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131149</t>
+          <t>130193</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>202568</t>
+          <t>205529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>258442</t>
+          <t>260076</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>203333</t>
+          <t>205925</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>234988</t>
+          <t>234289</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>854617</t>
+          <t>848386</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>903346</t>
+          <t>899305</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1066023</t>
+          <t>1066170</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1126663</t>
+          <t>1128338</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,81%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52157</t>
+          <t>52856</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83812</t>
+          <t>81220</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>172073</t>
+          <t>176114</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>220802</t>
+          <t>227033</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>235901</t>
+          <t>234226</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>296541</t>
+          <t>296394</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2611789</t>
+          <t>2614751</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2710941</t>
+          <t>2709011</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2833875</t>
+          <t>2837780</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2927970</t>
+          <t>2927701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5478794</t>
+          <t>5475051</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5607625</t>
+          <t>5609981</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,58%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>657379</t>
+          <t>659309</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>756531</t>
+          <t>753569</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>580764</t>
+          <t>581033</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>674859</t>
+          <t>670954</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1269429</t>
+          <t>1267073</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1398260</t>
+          <t>1402003</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2023</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2023 (tasa de respuesta: 98,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>252868</t>
+          <t>254422</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>299406</t>
+          <t>301378</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>208890</t>
+          <t>207848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>245035</t>
+          <t>244993</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>476582</t>
+          <t>476458</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>532724</t>
+          <t>537054</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199868</t>
+          <t>197896</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246406</t>
+          <t>244852</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>199053</t>
+          <t>199095</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>235198</t>
+          <t>236240</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>410638</t>
+          <t>406308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>466780</t>
+          <t>466904</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,49%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>262087</t>
+          <t>263629</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>306299</t>
+          <t>307749</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>225197</t>
+          <t>225339</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>256740</t>
+          <t>257884</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>499626</t>
+          <t>499713</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>553310</t>
+          <t>550906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,3%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>144196</t>
+          <t>142746</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>188408</t>
+          <t>186866</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>123678</t>
+          <t>122534</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>155221</t>
+          <t>155079</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>277602</t>
+          <t>280006</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>331286</t>
+          <t>331199</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90700</t>
+          <t>110307</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>425530</t>
+          <t>432057</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98693</t>
+          <t>97597</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117974</t>
+          <t>117807</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169397</t>
+          <t>149498</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>537273</t>
+          <t>536632</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,76%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>238609</t>
+          <t>232082</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>573439</t>
+          <t>553832</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46596</t>
+          <t>46763</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65877</t>
+          <t>66973</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>291436</t>
+          <t>292077</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>659312</t>
+          <t>679211</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>81,96%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>622754</t>
+          <t>624137</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>692834</t>
+          <t>689030</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>447056</t>
+          <t>447381</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>494627</t>
+          <t>495231</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1089593</t>
+          <t>1085629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1170957</t>
+          <t>1172638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,46%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>335914</t>
+          <t>339718</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>405994</t>
+          <t>404611</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>268056</t>
+          <t>267452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>315627</t>
+          <t>315302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>620474</t>
+          <t>618793</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>701838</t>
+          <t>705802</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>296487</t>
+          <t>297094</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>340355</t>
+          <t>342294</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>375352</t>
+          <t>386130</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>578118</t>
+          <t>579877</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>674803</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>894682</t>
+          <t>896659</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,05%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127576</t>
+          <t>125637</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171444</t>
+          <t>170837</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>252534</t>
+          <t>250775</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>455300</t>
+          <t>444522</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>403901</t>
+          <t>401924</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>617889</t>
+          <t>623780</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>48,04%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74282</t>
+          <t>75565</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124932</t>
+          <t>126715</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>446555</t>
+          <t>446221</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>498833</t>
+          <t>497816</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>529930</t>
+          <t>530515</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>605419</t>
+          <t>605764</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113920</t>
+          <t>112137</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>164570</t>
+          <t>163287</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>246001</t>
+          <t>247018</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>298279</t>
+          <t>298613</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>378267</t>
+          <t>377922</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>453756</t>
+          <t>453171</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,07%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1476817</t>
+          <t>1463950</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2068411</t>
+          <t>2067573</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1897158</t>
+          <t>1858732</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2104860</t>
+          <t>2105796</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3476881</t>
+          <t>3437115</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4140151</t>
+          <t>4129955</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,86%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1281027</t>
+          <t>1281865</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1872621</t>
+          <t>1885488</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1222385</t>
+          <t>1221449</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1430087</t>
+          <t>1468513</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2536532</t>
+          <t>2546728</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3199802</t>
+          <t>3239568</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57_AC_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57_AC_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>292090</t>
+          <t>289708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>335037</t>
+          <t>333903</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>182504</t>
+          <t>181669</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>217177</t>
+          <t>215809</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>483494</t>
+          <t>486313</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>539045</t>
+          <t>539914</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>137655</t>
+          <t>138789</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>180602</t>
+          <t>182984</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88352</t>
+          <t>89720</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123025</t>
+          <t>123860</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>239176</t>
+          <t>238307</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>294727</t>
+          <t>291908</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>206075</t>
+          <t>205625</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>244730</t>
+          <t>247097</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>226313</t>
+          <t>227266</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>262971</t>
+          <t>263752</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>443766</t>
+          <t>445702</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>497618</t>
+          <t>498828</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,66%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>120654</t>
+          <t>118287</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>159309</t>
+          <t>159759</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>108894</t>
+          <t>108113</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>145552</t>
+          <t>144599</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>239631</t>
+          <t>238421</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>293483</t>
+          <t>291547</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,55%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>365931</t>
+          <t>367585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>408983</t>
+          <t>410313</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104653</t>
+          <t>104631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127601</t>
+          <t>127431</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>481413</t>
+          <t>481184</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>531041</t>
+          <t>529698</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133406</t>
+          <t>132076</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>176458</t>
+          <t>174804</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39201</t>
+          <t>39371</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62149</t>
+          <t>62171</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>178150</t>
+          <t>179493</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>227778</t>
+          <t>228007</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>840661</t>
+          <t>841166</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>903540</t>
+          <t>906501</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>496298</t>
+          <t>498584</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>545499</t>
+          <t>545545</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1812,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>69,8%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>76,38%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1397711</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>1356668</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>1435639</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>71,58%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>69,48%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>76,37%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1374</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1397711</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1358447</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1440274</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>71,58%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>69,57%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,52%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>334794</t>
+          <t>331833</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>397673</t>
+          <t>397168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168786</t>
+          <t>168740</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>217987</t>
+          <t>215701</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1925,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>30,2%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>554909</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>516981</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>595952</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>28,42%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>26,48%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>30,52%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>554909</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>512346</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>594173</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>28,42%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>26,24%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>230694</t>
+          <t>229754</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>265166</t>
+          <t>265483</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>420331</t>
+          <t>418720</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>459754</t>
+          <t>459728</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>663184</t>
+          <t>663471</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>716066</t>
+          <t>715096</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,79%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85389</t>
+          <t>85072</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119861</t>
+          <t>120801</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108998</t>
+          <t>109024</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148421</t>
+          <t>150032</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>203241</t>
+          <t>204211</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>256123</t>
+          <t>255836</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>152062</t>
+          <t>151916</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>184642</t>
+          <t>185132</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>831534</t>
+          <t>829552</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>894204</t>
+          <t>893734</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>991449</t>
+          <t>993950</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1067722</t>
+          <t>1064387</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,81%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113559</t>
+          <t>113069</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>146139</t>
+          <t>146285</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>354556</t>
+          <t>355026</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>417226</t>
+          <t>419208</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>479238</t>
+          <t>482573</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>555511</t>
+          <t>553010</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2164272</t>
+          <t>2171362</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2272478</t>
+          <t>2273344</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2333578</t>
+          <t>2338967</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2437570</t>
+          <t>2442443</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4530105</t>
+          <t>4530046</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4685517</t>
+          <t>4681597</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,47%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>995078</t>
+          <t>994212</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1103284</t>
+          <t>1096194</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>938423</t>
+          <t>933550</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1042415</t>
+          <t>1037026</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1958032</t>
+          <t>1961952</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2113444</t>
+          <t>2113503</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>253895</t>
+          <t>254103</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>296733</t>
+          <t>297889</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190431</t>
+          <t>192367</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>226635</t>
+          <t>227955</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>457014</t>
+          <t>455574</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>513394</t>
+          <t>513104</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,65%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139430</t>
+          <t>138274</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>182268</t>
+          <t>182060</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84602</t>
+          <t>83282</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120806</t>
+          <t>118870</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>234006</t>
+          <t>234296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>290386</t>
+          <t>291826</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,05%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>251538</t>
+          <t>251756</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>293779</t>
+          <t>292426</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>217247</t>
+          <t>218988</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>252319</t>
+          <t>253364</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>481551</t>
+          <t>480408</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>536009</t>
+          <t>534357</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,14%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>122989</t>
+          <t>124342</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>165230</t>
+          <t>165012</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82029</t>
+          <t>80984</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117101</t>
+          <t>115360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>215108</t>
+          <t>216760</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>269566</t>
+          <t>270709</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>388124</t>
+          <t>386577</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>435708</t>
+          <t>436155</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>165518</t>
+          <t>163459</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>194910</t>
+          <t>195529</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>561434</t>
+          <t>561447</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>617736</t>
+          <t>615717</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,74%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>188014</t>
+          <t>187567</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>235598</t>
+          <t>237145</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64283</t>
+          <t>63664</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93675</t>
+          <t>95734</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265178</t>
+          <t>267197</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>321480</t>
+          <t>321467</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>750355</t>
+          <t>744240</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>814090</t>
+          <t>809555</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>568722</t>
+          <t>570228</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>616347</t>
+          <t>617710</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1332078</t>
+          <t>1328080</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1410372</t>
+          <t>1410447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,74%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>335014</t>
+          <t>339549</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>398749</t>
+          <t>404864</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>147314</t>
+          <t>145951</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>194939</t>
+          <t>193433</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>502393</t>
+          <t>502318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>580687</t>
+          <t>584685</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>333162</t>
+          <t>335585</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>374798</t>
+          <t>378178</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>549663</t>
+          <t>549909</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>599999</t>
+          <t>597247</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>896686</t>
+          <t>900724</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>960527</t>
+          <t>964791</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,47%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128583</t>
+          <t>125203</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170219</t>
+          <t>167796</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158305</t>
+          <t>161057</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>208641</t>
+          <t>208395</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>301159</t>
+          <t>296895</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>365000</t>
+          <t>360962</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>142334</t>
+          <t>142715</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>174258</t>
+          <t>175227</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>756422</t>
+          <t>760988</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>819600</t>
+          <t>820729</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>908097</t>
+          <t>915608</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>980999</t>
+          <t>980779</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,63%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90733</t>
+          <t>89764</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>122657</t>
+          <t>122276</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>284674</t>
+          <t>283545</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>347852</t>
+          <t>343286</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>388266</t>
+          <t>388486</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>461168</t>
+          <t>453657</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2202311</t>
+          <t>2198023</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2312745</t>
+          <t>2311220</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2526548</t>
+          <t>2523838</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2641447</t>
+          <t>2635296</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4760969</t>
+          <t>4753662</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4926007</t>
+          <t>4913703</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1081383</t>
+          <t>1082908</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1191817</t>
+          <t>1196105</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>889571</t>
+          <t>895722</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1004470</t>
+          <t>1007180</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1999140</t>
+          <t>2011444</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2164178</t>
+          <t>2171485</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>306896</t>
+          <t>307213</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>344199</t>
+          <t>344195</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>249853</t>
+          <t>249115</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>282294</t>
+          <t>280319</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>569074</t>
+          <t>567849</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>617213</t>
+          <t>615732</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,62%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84028</t>
+          <t>84032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>121331</t>
+          <t>121014</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>64758</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95224</t>
+          <t>95962</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156091</t>
+          <t>157572</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>204230</t>
+          <t>205455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>260613</t>
+          <t>260539</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>294364</t>
+          <t>293793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>272515</t>
+          <t>270123</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>304922</t>
+          <t>304241</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>539611</t>
+          <t>542030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>587639</t>
+          <t>589207</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,26%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78734</t>
+          <t>79305</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>112485</t>
+          <t>112559</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65385</t>
+          <t>66066</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97792</t>
+          <t>100184</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>155766</t>
+          <t>154198</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>203794</t>
+          <t>201375</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>420441</t>
+          <t>419320</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>454563</t>
+          <t>452920</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>129202</t>
+          <t>128742</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>147939</t>
+          <t>147710</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>557726</t>
+          <t>557529</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>596096</t>
+          <t>596239</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66385</t>
+          <t>68028</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100507</t>
+          <t>101628</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14645</t>
+          <t>14874</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33382</t>
+          <t>33842</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87436</t>
+          <t>87293</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125806</t>
+          <t>126003</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>877575</t>
+          <t>877606</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>931540</t>
+          <t>930115</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>663451</t>
+          <t>663527</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>705770</t>
+          <t>705015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1553431</t>
+          <t>1549951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1622183</t>
+          <t>1621318</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,49%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>211857</t>
+          <t>213282</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>265822</t>
+          <t>265791</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>116421</t>
+          <t>117176</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>158740</t>
+          <t>158664</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343405</t>
+          <t>344270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>412157</t>
+          <t>415637</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>477104</t>
+          <t>475860</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>517593</t>
+          <t>514969</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>602963</t>
+          <t>600370</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>640396</t>
+          <t>639692</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1088586</t>
+          <t>1089568</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1143133</t>
+          <t>1144361</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,85%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97913</t>
+          <t>100537</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>138402</t>
+          <t>139646</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92760</t>
+          <t>93464</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130193</t>
+          <t>132786</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>205529</t>
+          <t>204301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>260076</t>
+          <t>259094</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>205925</t>
+          <t>205282</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>234289</t>
+          <t>234716</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,47 +7733,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>81,74%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>877456</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>849646</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>902658</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>81,59%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>877456</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>848386</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>899305</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>81,59%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1066170</t>
+          <t>1066235</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1128338</t>
+          <t>1126415</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52856</t>
+          <t>52429</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81220</t>
+          <t>81863</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,47 +7846,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>18,26%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>28,51%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>197963</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>172761</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>225773</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>18,41%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>28,29%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>197963</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>176114</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>227033</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>18,41%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>234226</t>
+          <t>236149</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>296394</t>
+          <t>296329</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2614751</t>
+          <t>2612585</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2709011</t>
+          <t>2712376</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2837780</t>
+          <t>2835323</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2927701</t>
+          <t>2922050</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5475051</t>
+          <t>5471042</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5609981</t>
+          <t>5608386</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>659309</t>
+          <t>655944</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>753569</t>
+          <t>755735</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>581033</t>
+          <t>586684</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>670954</t>
+          <t>673411</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1267073</t>
+          <t>1268668</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1402003</t>
+          <t>1406012</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>277391</t>
+          <t>307769</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>254422</t>
+          <t>284821</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>301378</t>
+          <t>331014</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>227310</t>
+          <t>253150</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>207848</t>
+          <t>232614</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>244993</t>
+          <t>272772</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>504701</t>
+          <t>560919</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>476458</t>
+          <t>524949</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>537054</t>
+          <t>590023</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,36%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>221883</t>
+          <t>236834</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>197896</t>
+          <t>213589</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244852</t>
+          <t>259782</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>216778</t>
+          <t>230882</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>199095</t>
+          <t>211260</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>236240</t>
+          <t>251418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>438661</t>
+          <t>467716</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>406308</t>
+          <t>438612</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>466904</t>
+          <t>503686</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,97%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>499274</t>
+          <t>544603</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>499274</t>
+          <t>544603</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>499274</t>
+          <t>544603</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>444088</t>
+          <t>484032</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>444088</t>
+          <t>484032</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>444088</t>
+          <t>484032</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>943362</t>
+          <t>1028635</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>943362</t>
+          <t>1028635</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>943362</t>
+          <t>1028635</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>283740</t>
+          <t>310796</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>263629</t>
+          <t>288145</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>307749</t>
+          <t>333128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>242866</t>
+          <t>266685</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>225339</t>
+          <t>247326</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>257884</t>
+          <t>282548</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>526605</t>
+          <t>577481</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>499713</t>
+          <t>548699</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>550906</t>
+          <t>606567</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>67,26%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>166755</t>
+          <t>170670</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>142746</t>
+          <t>148338</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>186866</t>
+          <t>193321</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>137552</t>
+          <t>153660</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>122534</t>
+          <t>137797</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>155079</t>
+          <t>173019</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>304307</t>
+          <t>324330</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>280006</t>
+          <t>295244</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>331199</t>
+          <t>353112</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>450495</t>
+          <t>481466</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>450495</t>
+          <t>481466</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>450495</t>
+          <t>481466</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>380418</t>
+          <t>420345</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>380418</t>
+          <t>420345</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>380418</t>
+          <t>420345</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>830912</t>
+          <t>901811</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>830912</t>
+          <t>901811</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>830912</t>
+          <t>901811</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>263501</t>
+          <t>292524</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110307</t>
+          <t>271163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>432057</t>
+          <t>312134</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>108019</t>
+          <t>119289</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97597</t>
+          <t>107864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117807</t>
+          <t>130529</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>371521</t>
+          <t>411812</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149498</t>
+          <t>386208</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>536632</t>
+          <t>434418</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>66,72%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>400638</t>
+          <t>173638</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>232082</t>
+          <t>154028</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>553832</t>
+          <t>194999</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>56551</t>
+          <t>65647</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46763</t>
+          <t>54407</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66973</t>
+          <t>77072</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>457188</t>
+          <t>239285</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>292077</t>
+          <t>216679</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>679211</t>
+          <t>264889</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>664139</t>
+          <t>466162</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>664139</t>
+          <t>466162</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>664139</t>
+          <t>466162</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164570</t>
+          <t>184936</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164570</t>
+          <t>184936</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164570</t>
+          <t>184936</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>828709</t>
+          <t>651097</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>828709</t>
+          <t>651097</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>828709</t>
+          <t>651097</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>657384</t>
+          <t>728937</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>624137</t>
+          <t>692915</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>689030</t>
+          <t>765517</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>471230</t>
+          <t>538945</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>447381</t>
+          <t>514578</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>495231</t>
+          <t>561238</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1128615</t>
+          <t>1267882</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1085629</t>
+          <t>1223140</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1172638</t>
+          <t>1311702</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>371364</t>
+          <t>396538</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>339718</t>
+          <t>359958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>404611</t>
+          <t>432560</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>291453</t>
+          <t>310678</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>267452</t>
+          <t>288385</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>315302</t>
+          <t>335045</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>662816</t>
+          <t>707216</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>618793</t>
+          <t>663396</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>705802</t>
+          <t>751958</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>38,07%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1028748</t>
+          <t>1125475</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1028748</t>
+          <t>1125475</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1028748</t>
+          <t>1125475</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>762683</t>
+          <t>849623</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>762683</t>
+          <t>849623</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>762683</t>
+          <t>849623</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1791431</t>
+          <t>1975098</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1791431</t>
+          <t>1975098</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1791431</t>
+          <t>1975098</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>319015</t>
+          <t>382876</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>297094</t>
+          <t>356695</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>342294</t>
+          <t>405891</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>509675</t>
+          <t>582024</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>386130</t>
+          <t>560472</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>579877</t>
+          <t>603933</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>828691</t>
+          <t>964899</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>674803</t>
+          <t>932523</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>896659</t>
+          <t>998056</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>72,43%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>148916</t>
+          <t>175899</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125637</t>
+          <t>152884</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170837</t>
+          <t>202080</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>320977</t>
+          <t>237255</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>250775</t>
+          <t>215346</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>444522</t>
+          <t>258807</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>469892</t>
+          <t>413155</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>401924</t>
+          <t>379998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>623780</t>
+          <t>445531</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>467931</t>
+          <t>558775</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>467931</t>
+          <t>558775</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>467931</t>
+          <t>558775</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>830652</t>
+          <t>819279</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>830652</t>
+          <t>819279</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>830652</t>
+          <t>819279</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1298583</t>
+          <t>1378054</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1298583</t>
+          <t>1378054</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1298583</t>
+          <t>1378054</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>98622</t>
+          <t>105125</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75565</t>
+          <t>81593</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>126715</t>
+          <t>129097</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>473032</t>
+          <t>535501</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>446221</t>
+          <t>506020</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>497816</t>
+          <t>562724</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>571654</t>
+          <t>640626</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>530515</t>
+          <t>599115</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>605764</t>
+          <t>676441</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>140230</t>
+          <t>130258</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112137</t>
+          <t>106286</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>163287</t>
+          <t>153790</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>271802</t>
+          <t>293471</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>247018</t>
+          <t>266248</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>298613</t>
+          <t>322952</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>412032</t>
+          <t>423730</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>377922</t>
+          <t>387915</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>453171</t>
+          <t>465241</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>43,71%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>238852</t>
+          <t>235383</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>238852</t>
+          <t>235383</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>238852</t>
+          <t>235383</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>744834</t>
+          <t>828972</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>744834</t>
+          <t>828972</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>744834</t>
+          <t>828972</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>983686</t>
+          <t>1064356</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>983686</t>
+          <t>1064356</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>983686</t>
+          <t>1064356</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1899654</t>
+          <t>2128026</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1463950</t>
+          <t>2068625</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2067573</t>
+          <t>2191731</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2032133</t>
+          <t>2295593</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1858732</t>
+          <t>2242114</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2105796</t>
+          <t>2346461</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3931787</t>
+          <t>4423619</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3437115</t>
+          <t>4342249</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4129955</t>
+          <t>4514909</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>64,51%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1449784</t>
+          <t>1283837</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1281865</t>
+          <t>1220132</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1885488</t>
+          <t>1343238</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1295112</t>
+          <t>1291593</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1221449</t>
+          <t>1240725</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1468513</t>
+          <t>1345072</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2744896</t>
+          <t>2575431</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2546728</t>
+          <t>2484141</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3239568</t>
+          <t>2656801</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3349438</t>
+          <t>3411863</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3349438</t>
+          <t>3411863</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3349438</t>
+          <t>3411863</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3327245</t>
+          <t>3587186</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3327245</t>
+          <t>3587186</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3327245</t>
+          <t>3587186</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6676683</t>
+          <t>6999050</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6676683</t>
+          <t>6999050</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6676683</t>
+          <t>6999050</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
